--- a/output/pdf_financials_xlsx/GOK.xlsx
+++ b/output/pdf_financials_xlsx/GOK.xlsx
@@ -1081,7 +1081,7 @@
         <v>-1.203132</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.019019</v>
+        <v>-0.023951</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-0.596463</v>
@@ -1301,7 +1301,7 @@
         <v>-1.203132</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.021485</v>
+        <v>-0.021485</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.596278</v>
@@ -1430,7 +1430,7 @@
         <v>-1.203132</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.021485</v>
+        <v>-0.021485</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-0.596278</v>
@@ -1644,7 +1644,7 @@
         <v>-1.203132</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.019019</v>
+        <v>-0.023951</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-0.596463</v>
@@ -1730,7 +1730,7 @@
         <v>-1.204158</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.019019</v>
+        <v>-0.023951</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.596463</v>
@@ -1773,7 +1773,7 @@
         <v>-22.48682900375503</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.7589061440712628</v>
+        <v>-0.9557054028419377</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>-40.90995137140858</v>
@@ -1816,7 +1816,7 @@
         <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>12.96598138703402</v>
+        <v>-10.29602104296272</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0.03101617367716019</v>
@@ -1859,7 +1859,7 @@
         <v>-22.46766915383679</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.8573057734566002</v>
+        <v>-0.8573057734566002</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>-40.89726266983998</v>
@@ -4448,16 +4448,16 @@
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.429431</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.429431</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.429431</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.131995</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>-1.203132</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>0.021485</v>
+        <v>-0.021485</v>
       </c>
       <c r="M99" s="3" t="n">
         <v>-0.596278</v>
@@ -12440,7 +12440,11 @@
           <t>Reserves (Note 14)</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -13640,7 +13644,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -15088,7 +15096,11 @@
           <t>Reserves (note 10)</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -16138,7 +16150,11 @@
           <t>Reserves (note 7)</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -33438,7 +33454,7 @@
         </is>
       </c>
       <c r="O362" s="5" t="n">
-        <v>0.021485</v>
+        <v>-0.021485</v>
       </c>
       <c r="P362" s="5" t="n">
         <v>-0.596278</v>

--- a/output/pdf_financials_xlsx/GOK.xlsx
+++ b/output/pdf_financials_xlsx/GOK.xlsx
@@ -1879,25 +1879,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.056419</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.444271</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.422871</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.548752</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.965917</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.115309</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.515208</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0</v>
@@ -1965,25 +1965,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.056419</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.444271</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.422871</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.548752</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.965917</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.115309</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.515208</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0</v>
@@ -2481,25 +2481,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.445484</v>
+        <v>0.389065</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.865206</v>
+        <v>0.420935</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.041994</v>
+        <v>0.619123</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.764649</v>
+        <v>0.215897</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.131969</v>
+        <v>1.166052</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.591894</v>
+        <v>0.476585</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.447393</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.30399</v>
@@ -5829,10 +5829,10 @@
         <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.047504</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.04751</v>
       </c>
     </row>
     <row r="125">
@@ -5872,10 +5872,10 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.047504</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.04751</v>
       </c>
     </row>
     <row r="126">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
@@ -18740,7 +18740,11 @@
           <t>Principal elements of lease payments</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -39748,7 +39752,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">

--- a/output/pdf_financials_xlsx/GOK.xlsx
+++ b/output/pdf_financials_xlsx/GOK.xlsx
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0.413615</v>
@@ -1687,10 +1687,10 @@
         <v>-0.001026</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.047028</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.048971</v>
       </c>
     </row>
     <row r="29">
@@ -1712,7 +1712,7 @@
         <v>-0.492154</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.543053</v>
+        <v>-1.363053</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-2.557872</v>
@@ -1730,10 +1730,10 @@
         <v>-1.204158</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.023951</v>
+        <v>0.023077</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.596463</v>
+        <v>-0.547492</v>
       </c>
     </row>
     <row r="30">
@@ -1755,7 +1755,7 @@
         <v>-71.64501975444512</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-118.4308262626495</v>
+        <v>-104.6156502918456</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-226.2028127313101</v>
@@ -1773,10 +1773,10 @@
         <v>-22.48682900375503</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-0.9557054028419377</v>
+        <v>0.9208305950224791</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-40.90995137140858</v>
+        <v>-37.55114918483666</v>
       </c>
     </row>
     <row r="31">
@@ -4773,28 +4773,28 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.422668</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.037273</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.047241</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.024341</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.026893</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.091919</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.079418</v>
       </c>
     </row>
     <row r="101">
@@ -17734,7 +17734,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -17800,7 +17804,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -22564,7 +22572,11 @@
           <t>Depreciation of property, plant and equipment 37,273</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -22642,7 +22654,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -25024,7 +25036,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -25100,7 +25116,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -27192,7 +27208,11 @@
           <t>Amortization intangible assets</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -32804,7 +32824,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -32856,10 +32880,10 @@
         </is>
       </c>
       <c r="O354" s="5" t="n">
-        <v>-0.000778</v>
+        <v>0.000778</v>
       </c>
       <c r="P354" s="5" t="n">
-        <v>-0.001432</v>
+        <v>0.001432</v>
       </c>
     </row>
     <row r="355">
@@ -32878,7 +32902,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -32930,10 +32958,10 @@
         </is>
       </c>
       <c r="O355" s="5" t="n">
-        <v>-0.04625</v>
+        <v>0.04625</v>
       </c>
       <c r="P355" s="5" t="n">
-        <v>-0.047539</v>
+        <v>0.047539</v>
       </c>
     </row>
     <row r="356">

--- a/output/pdf_financials_xlsx/GOK.xlsx
+++ b/output/pdf_financials_xlsx/GOK.xlsx
@@ -682,22 +682,22 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="8">
@@ -814,19 +814,19 @@
         <v>6.820743</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="11">
@@ -866,10 +866,10 @@
         <v>-0.7755840000000001</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>1.154956</v>
+        <v>1.114956</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.537968</v>
+        <v>0.497968</v>
       </c>
     </row>
     <row r="12">
@@ -3212,25 +3212,25 @@
         <v>0</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.09433900000000001</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>1.243544</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>1.074497</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.115736</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.075068</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.011505</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.03844</v>
       </c>
     </row>
     <row r="65">
@@ -3341,10 +3341,10 @@
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.272656</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.428646</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0</v>
@@ -3356,10 +3356,10 @@
         <v>0</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.707869</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.770674</v>
       </c>
     </row>
     <row r="68">
@@ -3485,10 +3485,10 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.049116</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.024761</v>
       </c>
     </row>
     <row r="71">
@@ -3528,10 +3528,10 @@
         <v>0</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.049116</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.024761</v>
       </c>
     </row>
     <row r="72">
@@ -3700,10 +3700,10 @@
         <v>1.279256</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>2.863533</v>
+        <v>2.814417</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>3.154001</v>
+        <v>3.12924</v>
       </c>
     </row>
     <row r="76">
@@ -7396,7 +7396,11 @@
           <t>Lease liabilities 21</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -20164,7 +20168,11 @@
           <t>Proceed from private placement</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -21964,7 +21972,11 @@
           <t>Deferred tax expense/(recovery) 2,570</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -28124,7 +28136,11 @@
           <t>Deferred income tax (recovery)</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -31376,7 +31392,11 @@
           <t>Future income tax expense</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E334" s="5" t="n">
         <v>0.039164</v>
       </c>
@@ -32548,7 +32568,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -32580,22 +32604,22 @@
         </is>
       </c>
       <c r="K350" s="5" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="L350" s="5" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="M350" s="5" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="N350" s="5" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="O350" s="5" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="P350" s="5" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="351">
@@ -39248,7 +39272,11 @@
           <t>Directors’ fees (Note 17)</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
